--- a/Ozrit HR data/ozrit/HR/Salary/Attendance Percentage/Leaves management_.xlsx
+++ b/Ozrit HR data/ozrit/HR/Salary/Attendance Percentage/Leaves management_.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixld\Downloads\ozrit\Ozrit HR data\ozrit\HR\Salary\Attendance Percentage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\HR\Salary\Attendance Percentage\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A10D7A-8F44-42E5-82B5-1D1A1146DCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7190" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paid Leaves " sheetId="1" r:id="rId1"/>
     <sheet name="Unpaid leaves " sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="201">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -620,12 +621,15 @@
   </si>
   <si>
     <t>7(3medical+3emergency+1 casual)</t>
+  </si>
+  <si>
+    <t>10.5(2paid leaves+4 emergency)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1107,7 +1111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1472,11 +1476,21 @@
       <c r="G9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="H9" s="10">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10">
+        <v>1</v>
+      </c>
+      <c r="J9" s="10">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>200</v>
+      </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
@@ -8134,7 +8148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z983"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
